--- a/templates/000_pm_suite/02_프로젝트 개발/04_설계/03_개발설계/프로젝트명_일정계획서(개발)_V1.0_20230530.xlsx
+++ b/templates/000_pm_suite/02_프로젝트 개발/04_설계/03_개발설계/프로젝트명_일정계획서(개발)_V1.0_20230530.xlsx
@@ -521,7 +521,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>[PM-48] SyncGuard AI 스프린트별 상세 개발 일정계획서 (Development Sprint Schedule) — 주식회사 한빛글로벌 SyncGuard AI 시스템 구축</t>
+          <t>[PM-48] SyncFlow AI 스프린트별 상세 개발 일정계획서 (Development Sprint Schedule) — 주식회사 한빛글로벌 SyncFlow AI 시스템 구축</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>PDF/이미지 업로드 S3 스트리밍 및 Upstage/Clova OCR 좌표 변환기</t>
+          <t>PDF/이미지 업로드 S3 스트리밍 및 EnterpriseVision/Enterprise Vision OCR 좌표 변환기</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>사용자 심의 대시보드, 멀티모달 업로드 및 OCR 바운딩박스 인라인 교정 뷰어</t>
+          <t>사용자 검증 대시보드, 멀티모달 업로드 및 OCR 바운딩박스 인라인 교정 뷰어</t>
         </is>
       </c>
       <c r="E8" s="9" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>법령 위반 판정, 근거 조항 매핑 및 안전 대체문구 3안 생성 체인</t>
+          <t>법령 위반 판정, 근거 조항 매핑 및 안전 표준수정조항 3안 생성 체인</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">
@@ -914,7 +914,7 @@
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>ProductLab 전성분 마스터 02:00 일배치 동기화 및 배합한도 비교기</t>
+          <t>PLM-Nexus 자재BOM 마스터 02:00 일배치 동기화 및 유해물질한도 비교기</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>심의 결과 PDF 리포트 생성기 및 MarketingHub Webhook 콜백 발송기</t>
+          <t>검증 결과 PDF 리포트 생성기 및 SRM-Portal Webhook 콜백 발송기</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
